--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -633,7 +633,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -667,7 +667,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -701,7 +701,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -828,7 +828,7 @@
         <v>4</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -862,7 +862,7 @@
         <v>4</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -927,7 +927,7 @@
         <v>4</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -961,7 +961,7 @@
         <v>4</v>
       </c>
       <c r="H29">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1026,7 +1026,7 @@
         <v>3</v>
       </c>
       <c r="H31">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1366,7 +1366,7 @@
         <v>4</v>
       </c>
       <c r="H41">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -1431,7 +1431,7 @@
         <v>3</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1496,7 +1496,7 @@
         <v>3</v>
       </c>
       <c r="H45">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -1632,7 +1632,7 @@
         <v>3</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -1666,7 +1666,7 @@
         <v>3</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -1700,7 +1700,7 @@
         <v>3</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -1734,7 +1734,7 @@
         <v>3</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -1768,7 +1768,7 @@
         <v>3</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -1802,7 +1802,7 @@
         <v>3</v>
       </c>
       <c r="H54">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1836,7 +1836,7 @@
         <v>3</v>
       </c>
       <c r="H55">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -1901,7 +1901,7 @@
         <v>4</v>
       </c>
       <c r="H57">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -1935,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="H58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>4</v>
       </c>
       <c r="H59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>3</v>
       </c>
       <c r="H60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2051,6 +2051,9 @@
       <c r="G61">
         <v>3</v>
       </c>
+      <c r="H61">
+        <v>4</v>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">ring;amulet</t>
@@ -2088,7 +2091,7 @@
         <v>3</v>
       </c>
       <c r="H62">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -2122,7 +2125,7 @@
         <v>3</v>
       </c>
       <c r="H63">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -1632,7 +1632,7 @@
         <v>3</v>
       </c>
       <c r="H49">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1666,7 +1666,7 @@
         <v>3</v>
       </c>
       <c r="H50">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -1700,7 +1700,7 @@
         <v>3</v>
       </c>
       <c r="H51">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -1734,7 +1734,7 @@
         <v>3</v>
       </c>
       <c r="H52">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -1768,7 +1768,7 @@
         <v>3</v>
       </c>
       <c r="H53">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1802,7 +1802,7 @@
         <v>3</v>
       </c>
       <c r="H54">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -1813,19 +1813,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">ccRed</t>
+          <t xml:space="preserve">resAll</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">控制時間縮減%</t>
+          <t xml:space="preserve">全屬性抗性%</t>
         </is>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>0.02</v>
+        <v>0.005</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1847,19 +1847,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">moveSpeed</t>
+          <t xml:space="preserve">ccRed</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">移動速度%</t>
+          <t xml:space="preserve">控制時間縮減%</t>
         </is>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E56">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1867,6 +1867,9 @@
         </is>
       </c>
       <c r="G56">
+        <v>3</v>
+      </c>
+      <c r="H56">
         <v>4</v>
       </c>
     </row>
@@ -1878,19 +1881,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">loot</t>
+          <t xml:space="preserve">moveSpeed</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">掉寶率%</t>
+          <t xml:space="preserve">移動速度%</t>
         </is>
       </c>
       <c r="D57">
         <v>3</v>
       </c>
       <c r="E57">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1898,9 +1901,6 @@
         </is>
       </c>
       <c r="G57">
-        <v>4</v>
-      </c>
-      <c r="H57">
         <v>4</v>
       </c>
     </row>
@@ -1912,19 +1912,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">xpBonus</t>
+          <t xml:space="preserve">loot</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">經驗加成%</t>
+          <t xml:space="preserve">掉寶率%</t>
         </is>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -1936,11 +1936,6 @@
       </c>
       <c r="H58">
         <v>4</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ring;amulet</t>
-        </is>
       </c>
     </row>
     <row r="59">
@@ -1951,19 +1946,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">goldBonus</t>
+          <t xml:space="preserve">xpBonus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成%</t>
+          <t xml:space="preserve">經驗加成%</t>
         </is>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E59">
-        <v>0.025</v>
+        <v>0.02</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -1990,27 +1985,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">luck</t>
+          <t xml:space="preserve">goldBonus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">幸運值</t>
+          <t xml:space="preserve">金幣加成%</t>
         </is>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E60">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">FALSE</t>
+          <t xml:space="preserve">TRUE</t>
         </is>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60">
         <v>4</v>
@@ -2029,19 +2024,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">weight</t>
+          <t xml:space="preserve">luck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">負重上限</t>
+          <t xml:space="preserve">幸運值</t>
         </is>
       </c>
       <c r="D61">
         <v>2</v>
       </c>
       <c r="E61">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2068,23 +2063,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">enhanceSuccess</t>
+          <t xml:space="preserve">weight</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">強化成功率%</t>
+          <t xml:space="preserve">負重上限</t>
         </is>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62">
-        <v>0.015</v>
+        <v>0.3</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">FALSE</t>
         </is>
       </c>
       <c r="G62">
@@ -2092,6 +2087,11 @@
       </c>
       <c r="H62">
         <v>4</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ring;amulet</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">decomposeYield</t>
+          <t xml:space="preserve">enhanceSuccess</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">分解高產率%</t>
+          <t xml:space="preserve">強化成功率%</t>
         </is>
       </c>
       <c r="D63">
@@ -2136,19 +2136,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">hybridMutation</t>
+          <t xml:space="preserve">decomposeYield</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">合成變異率%</t>
+          <t xml:space="preserve">分解高產率%</t>
         </is>
       </c>
       <c r="D64">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H64">
         <v>4</v>
@@ -2170,23 +2170,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">enrageThreshold</t>
+          <t xml:space="preserve">hybridMutation</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">狂暴閾值+</t>
+          <t xml:space="preserve">合成變異率%</t>
         </is>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E65">
-        <v>0.08</v>
+        <v>0.012</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">FALSE</t>
+          <t xml:space="preserve">TRUE</t>
         </is>
       </c>
       <c r="G65">
@@ -2204,23 +2204,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">affixCap</t>
+          <t xml:space="preserve">enrageThreshold</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">詞條上限率%</t>
+          <t xml:space="preserve">狂暴閾值+</t>
         </is>
       </c>
       <c r="D66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66">
-        <v>0.015</v>
+        <v>0.08</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t xml:space="preserve">FALSE</t>
         </is>
       </c>
       <c r="G66">
@@ -2229,11 +2229,6 @@
       <c r="H66">
         <v>4</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ring;amulet</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2243,19 +2238,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">gemEff</t>
+          <t xml:space="preserve">affixCap</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">寶石鑲嵌效率%</t>
+          <t xml:space="preserve">詞條上限率%</t>
         </is>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E67">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2277,28 +2272,39 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">特殊被動</t>
+          <t xml:space="preserve">詞條池</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">sunder</t>
+          <t xml:space="preserve">gemEff</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">破甲</t>
+          <t xml:space="preserve">寶石鑲嵌效率%</t>
         </is>
       </c>
       <c r="D68">
-        <v>10</v>
-      </c>
-      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="E68">
+        <v>0.025</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TRUE</t>
+        </is>
+      </c>
+      <c r="G68">
         <v>2</v>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">攻擊時忽略目標 {v}% 防禦</t>
+      <c r="H68">
+        <v>4</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ring;amulet</t>
         </is>
       </c>
     </row>
@@ -2310,23 +2316,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">thorns</t>
+          <t xml:space="preserve">sunder</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">反震</t>
+          <t xml:space="preserve">破甲</t>
         </is>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">受擊時對敵人造成自身 {v}% 最大生命的傷害</t>
+          <t xml:space="preserve">攻擊時忽略目標 {v}% 防禦</t>
         </is>
       </c>
     </row>
@@ -2338,23 +2344,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">doubleHit</t>
+          <t xml:space="preserve">thorns</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">連擊</t>
+          <t xml:space="preserve">反震</t>
         </is>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率再次攻擊</t>
+          <t xml:space="preserve">受擊時對敵人造成自身 {v}% 最大生命的傷害</t>
         </is>
       </c>
     </row>
@@ -2366,23 +2372,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">stun</t>
+          <t xml:space="preserve">doubleHit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">暈眩</t>
+          <t xml:space="preserve">連擊</t>
         </is>
       </c>
       <c r="D71">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J71">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率暈眩敵人 1 秒</t>
+          <t xml:space="preserve">攻擊時有 {v}% 機率再次攻擊</t>
         </is>
       </c>
     </row>
@@ -2394,23 +2400,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">slowHit</t>
+          <t xml:space="preserve">stun</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">減速</t>
+          <t xml:space="preserve">暈眩</t>
         </is>
       </c>
       <c r="D72">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J72">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率使敵人攻速降低 30%，持續 3 秒</t>
+          <t xml:space="preserve">攻擊時有 {v}% 機率暈眩敵人 1 秒</t>
         </is>
       </c>
     </row>
@@ -2422,23 +2428,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">trueDmg</t>
+          <t xml:space="preserve">slowHit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">真傷</t>
+          <t xml:space="preserve">減速</t>
         </is>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J73">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t xml:space="preserve">每次攻擊附加 {v}% 攻擊力的真實傷害</t>
+          <t xml:space="preserve">攻擊時有 {v}% 機率使敵人攻速降低 30%，持續 3 秒</t>
         </is>
       </c>
     </row>
@@ -2450,53 +2456,51 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">soulEater</t>
+          <t xml:space="preserve">trueDmg</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">吸魂</t>
+          <t xml:space="preserve">真傷</t>
         </is>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J74">
         <v>1.5</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t xml:space="preserve">擊殺敵人時回復 {v}% 最大生命</t>
+          <t xml:space="preserve">每次攻擊附加 {v}% 攻擊力的真實傷害</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">特殊被動</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">soulEater</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">吸魂</t>
         </is>
       </c>
       <c r="D75">
-        <v>25</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="J75">
+        <v>1.5</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">擊殺敵人時回復 {v}% 最大生命</t>
         </is>
       </c>
     </row>
@@ -2508,25 +2512,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D76">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
+          <t xml:space="preserve">hpPct</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -2538,25 +2542,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">godMight</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">神力</t>
         </is>
       </c>
       <c r="D77">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">aspdPct</t>
+          <t xml:space="preserve">atkPct;matkPct</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -2568,25 +2572,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">godHaste</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">神速</t>
         </is>
       </c>
       <c r="D78">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
+          <t xml:space="preserve">aspdPct</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -2598,25 +2602,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">godSlayer</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">屠神</t>
         </is>
       </c>
       <c r="D79">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">goldBonus;loot</t>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -2628,12 +2632,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">greed</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">貪婪</t>
         </is>
       </c>
       <c r="D80">
@@ -2641,12 +2645,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
+          <t xml:space="preserve">goldBonus;loot</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -2658,20 +2662,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">godWall</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">神壁</t>
         </is>
       </c>
       <c r="D81">
-        <v>12</v>
+        <v>25</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -2683,20 +2692,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">smite</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">天罰</t>
         </is>
       </c>
       <c r="D82">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
         </is>
       </c>
     </row>
@@ -2708,20 +2717,20 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">annihilate</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">破滅</t>
         </is>
       </c>
       <c r="D83">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
         </is>
       </c>
     </row>
@@ -2733,20 +2742,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">sanctuary</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">聖佑</t>
         </is>
       </c>
       <c r="D84">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
         </is>
       </c>
     </row>
@@ -2758,20 +2767,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">undying</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">不朽</t>
         </is>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
         </is>
       </c>
     </row>
@@ -2783,18 +2792,43 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>5</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D86">
+      <c r="D87">
         <v>35</v>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,17 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\develop\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A2FA95-7226-4FB1-8351-D739C88E320E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DD5511-A703-4249-BC97-8B29F81A33B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1510,9 +1523,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R125"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.25">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1568,7 +1584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="14.25">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1597,7 +1613,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="14.25">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1626,7 +1642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="14.25">
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1655,7 +1671,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="14.25">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1684,7 +1700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="14.25">
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1713,7 +1729,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="14.25">
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1742,7 +1758,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="14.25">
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1771,7 +1787,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="14.25">
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1800,7 +1816,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="14.25">
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1829,7 +1845,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="14.25">
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1858,7 +1874,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="14.25">
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1887,7 +1903,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="14.25">
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1916,7 +1932,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="14.25">
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1945,7 +1961,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="14.25">
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1974,7 +1990,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="14.25">
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2003,7 +2019,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.25">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2032,7 +2048,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.25">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2061,7 +2077,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.25">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2093,7 +2109,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.25">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2104,10 +2120,10 @@
         <v>62</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -2125,7 +2141,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.25">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -2136,10 +2152,10 @@
         <v>65</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="F21" t="s">
         <v>21</v>
@@ -2157,7 +2173,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14.25">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -2168,10 +2184,10 @@
         <v>67</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="F22" t="s">
         <v>21</v>
@@ -2189,7 +2205,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="14.25">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2218,7 +2234,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.25">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -2247,7 +2263,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="14.25">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -2276,7 +2292,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="14.25">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2308,7 +2324,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.25">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2340,7 +2356,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14.25">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -2369,7 +2385,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.25">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -2401,7 +2417,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.25">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -2433,7 +2449,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14.25">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -2462,7 +2478,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.25">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -2494,7 +2510,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="14.25">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -2526,7 +2542,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14.25">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -2558,7 +2574,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="14.25">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -2590,7 +2606,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="14.25">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -2619,7 +2635,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.25">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -2648,7 +2664,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.25">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -2677,7 +2693,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="14.25">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -2706,7 +2722,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="14.25">
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -2735,7 +2751,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.25">
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -2764,7 +2780,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.25">
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -2793,7 +2809,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.25">
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -2822,7 +2838,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.25">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -2851,7 +2867,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14.25">
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -2880,7 +2896,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.25">
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2909,7 +2925,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="14.25">
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -2938,7 +2954,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.25">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -2970,7 +2986,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="14.25">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -2999,7 +3015,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14.25">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -3031,7 +3047,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="14.25">
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -3060,7 +3076,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="14.25">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -3092,7 +3108,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="14.25">
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -3124,7 +3140,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="14.25">
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -3135,10 +3151,10 @@
         <v>141</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E54">
-        <v>8.0000000000000002E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F54" t="s">
         <v>25</v>
@@ -3156,7 +3172,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="14.25">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -3167,10 +3183,10 @@
         <v>143</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E55">
-        <v>8.0000000000000002E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F55" t="s">
         <v>25</v>
@@ -3188,7 +3204,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="14.25">
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -3199,10 +3215,10 @@
         <v>145</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E56">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F56" t="s">
         <v>25</v>
@@ -3220,7 +3236,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="14.25">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -3231,10 +3247,10 @@
         <v>147</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E57">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F57" t="s">
         <v>25</v>
@@ -3252,7 +3268,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="14.25">
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -3263,10 +3279,10 @@
         <v>149</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E58">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F58" t="s">
         <v>25</v>
@@ -3284,7 +3300,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="14.25">
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -3295,10 +3311,10 @@
         <v>151</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E59">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F59" t="s">
         <v>25</v>
@@ -3316,7 +3332,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="14.25">
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -3327,10 +3343,10 @@
         <v>153</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E60">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F60" t="s">
         <v>25</v>
@@ -3348,7 +3364,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="14.25">
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -3359,10 +3375,10 @@
         <v>155</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E61">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F61" t="s">
         <v>25</v>
@@ -3380,7 +3396,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="14.25">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -3391,10 +3407,10 @@
         <v>157</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E62">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="F62" t="s">
         <v>25</v>
@@ -3409,7 +3425,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14.25">
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -3441,7 +3457,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="14.25">
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -3470,7 +3486,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="14.25">
+    <row r="65" spans="1:13">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -3502,7 +3518,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="14.25">
+    <row r="66" spans="1:13">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -3534,7 +3550,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="14.25">
+    <row r="67" spans="1:13">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -3566,7 +3582,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="14.25">
+    <row r="68" spans="1:13">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -3598,7 +3614,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="14.25">
+    <row r="69" spans="1:13">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -3630,7 +3646,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="14.25">
+    <row r="70" spans="1:13">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -3662,7 +3678,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="14.25">
+    <row r="71" spans="1:13">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -3694,7 +3710,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="14.25">
+    <row r="72" spans="1:13">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -3726,7 +3742,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="14.25">
+    <row r="73" spans="1:13">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -3758,7 +3774,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="14.25">
+    <row r="74" spans="1:13">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -3790,7 +3806,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="14.25">
+    <row r="75" spans="1:13">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -3822,7 +3838,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="14.25">
+    <row r="76" spans="1:13">
       <c r="A76" t="s">
         <v>187</v>
       </c>
@@ -3842,7 +3858,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="14.25">
+    <row r="77" spans="1:13">
       <c r="A77" t="s">
         <v>187</v>
       </c>
@@ -3862,7 +3878,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="14.25">
+    <row r="78" spans="1:13">
       <c r="A78" t="s">
         <v>187</v>
       </c>
@@ -3882,7 +3898,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="14.25">
+    <row r="79" spans="1:13">
       <c r="A79" t="s">
         <v>187</v>
       </c>
@@ -3902,7 +3918,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="14.25">
+    <row r="80" spans="1:13">
       <c r="A80" t="s">
         <v>187</v>
       </c>
@@ -3922,7 +3938,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="14.25">
+    <row r="81" spans="1:18">
       <c r="A81" t="s">
         <v>187</v>
       </c>
@@ -3942,7 +3958,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="14.25">
+    <row r="82" spans="1:18">
       <c r="A82" t="s">
         <v>187</v>
       </c>
@@ -3962,7 +3978,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="14.25">
+    <row r="83" spans="1:18">
       <c r="A83" t="s">
         <v>187</v>
       </c>
@@ -3994,7 +4010,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="14.25">
+    <row r="84" spans="1:18">
       <c r="A84" t="s">
         <v>187</v>
       </c>
@@ -4020,7 +4036,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="14.25">
+    <row r="85" spans="1:18">
       <c r="A85" t="s">
         <v>187</v>
       </c>
@@ -4049,7 +4065,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="14.25">
+    <row r="86" spans="1:18">
       <c r="A86" t="s">
         <v>187</v>
       </c>
@@ -4078,7 +4094,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="14.25">
+    <row r="87" spans="1:18">
       <c r="A87" t="s">
         <v>187</v>
       </c>
@@ -4107,7 +4123,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="14.25">
+    <row r="88" spans="1:18">
       <c r="A88" t="s">
         <v>187</v>
       </c>
@@ -4133,7 +4149,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="14.25">
+    <row r="89" spans="1:18">
       <c r="A89" t="s">
         <v>187</v>
       </c>
@@ -4159,7 +4175,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="14.25">
+    <row r="90" spans="1:18">
       <c r="A90" t="s">
         <v>187</v>
       </c>
@@ -4185,7 +4201,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="14.25">
+    <row r="91" spans="1:18">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -4211,7 +4227,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="14.25">
+    <row r="92" spans="1:18">
       <c r="A92" t="s">
         <v>187</v>
       </c>
@@ -4243,7 +4259,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="14.25">
+    <row r="93" spans="1:18">
       <c r="A93" t="s">
         <v>187</v>
       </c>
@@ -4275,7 +4291,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="14.25">
+    <row r="94" spans="1:18">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -4304,7 +4320,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="14.25">
+    <row r="95" spans="1:18">
       <c r="A95" t="s">
         <v>187</v>
       </c>
@@ -4333,7 +4349,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="14.25">
+    <row r="96" spans="1:18">
       <c r="A96" t="s">
         <v>187</v>
       </c>
@@ -4362,7 +4378,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="14.25">
+    <row r="97" spans="1:18">
       <c r="A97" t="s">
         <v>187</v>
       </c>
@@ -4391,7 +4407,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="14.25">
+    <row r="98" spans="1:18">
       <c r="A98" t="s">
         <v>187</v>
       </c>
@@ -4423,7 +4439,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="14.25">
+    <row r="99" spans="1:18">
       <c r="A99" t="s">
         <v>187</v>
       </c>
@@ -4452,7 +4468,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="14.25">
+    <row r="100" spans="1:18">
       <c r="A100" t="s">
         <v>187</v>
       </c>
@@ -4481,7 +4497,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="14.25">
+    <row r="101" spans="1:18">
       <c r="A101" t="s">
         <v>187</v>
       </c>
@@ -4516,7 +4532,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="14.25">
+    <row r="102" spans="1:18">
       <c r="A102" t="s">
         <v>187</v>
       </c>
@@ -4548,7 +4564,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="14.25">
+    <row r="103" spans="1:18">
       <c r="A103" t="s">
         <v>187</v>
       </c>
@@ -4577,7 +4593,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="14.25">
+    <row r="104" spans="1:18">
       <c r="A104" t="s">
         <v>187</v>
       </c>
@@ -4606,7 +4622,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="14.25">
+    <row r="105" spans="1:18">
       <c r="A105" t="s">
         <v>187</v>
       </c>
@@ -4638,7 +4654,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="14.25">
+    <row r="106" spans="1:18">
       <c r="A106" t="s">
         <v>187</v>
       </c>
@@ -4670,7 +4686,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="14.25">
+    <row r="107" spans="1:18">
       <c r="A107" t="s">
         <v>187</v>
       </c>
@@ -4699,7 +4715,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="14.25">
+    <row r="108" spans="1:18">
       <c r="A108" t="s">
         <v>187</v>
       </c>
@@ -4728,7 +4744,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="14.25">
+    <row r="109" spans="1:18">
       <c r="A109" t="s">
         <v>187</v>
       </c>
@@ -4757,7 +4773,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="14.25">
+    <row r="110" spans="1:18">
       <c r="A110" t="s">
         <v>187</v>
       </c>
@@ -4789,7 +4805,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="14.25">
+    <row r="111" spans="1:18">
       <c r="A111" t="s">
         <v>187</v>
       </c>
@@ -4821,7 +4837,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="14.25">
+    <row r="112" spans="1:18">
       <c r="A112" t="s">
         <v>187</v>
       </c>
@@ -4847,7 +4863,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="14.25">
+    <row r="113" spans="1:18">
       <c r="A113" t="s">
         <v>187</v>
       </c>
@@ -4873,7 +4889,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="14.25">
+    <row r="114" spans="1:18">
       <c r="A114" t="s">
         <v>361</v>
       </c>
@@ -4893,7 +4909,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="14.25">
+    <row r="115" spans="1:18">
       <c r="A115" t="s">
         <v>361</v>
       </c>
@@ -4913,7 +4929,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="14.25">
+    <row r="116" spans="1:18">
       <c r="A116" t="s">
         <v>361</v>
       </c>
@@ -4933,7 +4949,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="14.25">
+    <row r="117" spans="1:18">
       <c r="A117" t="s">
         <v>361</v>
       </c>
@@ -4953,7 +4969,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="14.25">
+    <row r="118" spans="1:18">
       <c r="A118" t="s">
         <v>361</v>
       </c>
@@ -4973,7 +4989,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="14.25">
+    <row r="119" spans="1:18">
       <c r="A119" t="s">
         <v>361</v>
       </c>
@@ -4993,7 +5009,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="14.25">
+    <row r="120" spans="1:18">
       <c r="A120" t="s">
         <v>361</v>
       </c>
@@ -5010,7 +5026,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="14.25">
+    <row r="121" spans="1:18">
       <c r="A121" t="s">
         <v>361</v>
       </c>
@@ -5027,7 +5043,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="14.25">
+    <row r="122" spans="1:18">
       <c r="A122" t="s">
         <v>361</v>
       </c>
@@ -5044,7 +5060,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="14.25">
+    <row r="123" spans="1:18">
       <c r="A123" t="s">
         <v>361</v>
       </c>
@@ -5061,7 +5077,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="14.25">
+    <row r="124" spans="1:18">
       <c r="A124" t="s">
         <v>361</v>
       </c>
@@ -5078,7 +5094,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="14.25">
+    <row r="125" spans="1:18">
       <c r="A125" t="s">
         <v>361</v>
       </c>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\develop\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A2FA95-7226-4FB1-8351-D739C88E320E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1962AE34-860D-443A-9390-254D66BA84B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equipment_Affix" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1257,7 +1270,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1265,6 +1278,7 @@
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1510,9 +1524,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R125"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1568,7 +1585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="14.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1597,7 +1614,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="14.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1626,7 +1643,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="14.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1655,7 +1672,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="14.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1684,7 +1701,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="14.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1713,7 +1730,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="14.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1742,7 +1759,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="14.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1771,7 +1788,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="14.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1800,7 +1817,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="14.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1829,7 +1846,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="14.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1858,7 +1875,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="14.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1887,7 +1904,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="14.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1916,7 +1933,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="14.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1945,7 +1962,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="14.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -1974,7 +1991,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="14.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2003,7 +2020,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2032,7 +2049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2061,7 +2078,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2093,7 +2110,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2125,7 +2142,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -2157,7 +2174,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -2189,7 +2206,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="14.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2218,7 +2235,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -2247,7 +2264,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="14.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -2276,7 +2293,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="14.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2308,7 +2325,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2340,7 +2357,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -2369,7 +2386,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -2401,7 +2418,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="14.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -2433,7 +2450,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -2462,7 +2479,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -2494,7 +2511,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="14.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -2526,7 +2543,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -2558,7 +2575,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="14.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -2590,7 +2607,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="14.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -2619,7 +2636,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="14.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -2648,7 +2665,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="14.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -2677,7 +2694,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="14.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -2706,7 +2723,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="14.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -2735,7 +2752,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="14.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -2764,7 +2781,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="14.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -2793,7 +2810,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="14.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -2822,7 +2839,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="14.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -2851,7 +2868,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="14.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -2880,7 +2897,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -2909,7 +2926,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="14.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -2938,7 +2955,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="14.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -2970,7 +2987,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="14.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -2999,7 +3016,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="14.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -3031,7 +3048,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="14.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -3060,7 +3077,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="14.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -3092,7 +3109,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="14.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -3124,7 +3141,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="14.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -3135,10 +3152,10 @@
         <v>141</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E54">
-        <v>8.0000000000000002E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F54" t="s">
         <v>25</v>
@@ -3156,7 +3173,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="14.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -3167,10 +3184,10 @@
         <v>143</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E55">
-        <v>8.0000000000000002E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F55" t="s">
         <v>25</v>
@@ -3188,7 +3205,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="14.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -3199,10 +3216,10 @@
         <v>145</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E56">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F56" t="s">
         <v>25</v>
@@ -3220,7 +3237,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="14.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -3231,10 +3248,10 @@
         <v>147</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E57">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F57" t="s">
         <v>25</v>
@@ -3252,7 +3269,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="14.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -3263,10 +3280,10 @@
         <v>149</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E58">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F58" t="s">
         <v>25</v>
@@ -3284,7 +3301,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="14.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -3295,10 +3312,10 @@
         <v>151</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E59">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F59" t="s">
         <v>25</v>
@@ -3316,7 +3333,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="14.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -3327,10 +3344,10 @@
         <v>153</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E60">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F60" t="s">
         <v>25</v>
@@ -3348,7 +3365,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="14.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -3359,10 +3376,10 @@
         <v>155</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E61">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F61" t="s">
         <v>25</v>
@@ -3380,7 +3397,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="14.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -3391,10 +3408,10 @@
         <v>157</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62">
-        <v>5.0000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="F62" t="s">
         <v>25</v>
@@ -3409,7 +3426,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="14.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -3441,7 +3458,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="14.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -3470,7 +3487,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="14.25">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -3502,7 +3519,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="14.25">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -3534,7 +3551,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="14.25">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -3566,7 +3583,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="14.25">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -3598,7 +3615,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="14.25">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -3630,7 +3647,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="14.25">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -3662,7 +3679,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="14.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -3694,7 +3711,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="14.25">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -3726,7 +3743,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="14.25">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -3758,7 +3775,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="14.25">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -3790,7 +3807,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="14.25">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -3822,7 +3839,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="14.25">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>187</v>
       </c>
@@ -3842,7 +3859,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="14.25">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>187</v>
       </c>
@@ -3862,7 +3879,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="14.25">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>187</v>
       </c>
@@ -3882,7 +3899,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="14.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>187</v>
       </c>
@@ -3902,7 +3919,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="14.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>187</v>
       </c>
@@ -3922,7 +3939,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="14.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>187</v>
       </c>
@@ -3942,7 +3959,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="14.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>187</v>
       </c>
@@ -3962,7 +3979,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="14.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>187</v>
       </c>
@@ -3994,7 +4011,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="14.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>187</v>
       </c>
@@ -4020,7 +4037,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="14.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>187</v>
       </c>
@@ -4049,7 +4066,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="14.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>187</v>
       </c>
@@ -4078,7 +4095,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="14.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>187</v>
       </c>
@@ -4107,7 +4124,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="14.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>187</v>
       </c>
@@ -4133,7 +4150,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="14.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>187</v>
       </c>
@@ -4159,7 +4176,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="14.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>187</v>
       </c>
@@ -4185,7 +4202,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="14.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -4211,7 +4228,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="14.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>187</v>
       </c>
@@ -4243,7 +4260,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="14.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>187</v>
       </c>
@@ -4275,7 +4292,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="14.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>187</v>
       </c>
@@ -4304,7 +4321,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="14.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>187</v>
       </c>
@@ -4333,7 +4350,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="14.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>187</v>
       </c>
@@ -4362,7 +4379,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="14.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>187</v>
       </c>
@@ -4391,7 +4408,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="14.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>187</v>
       </c>
@@ -4423,7 +4440,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="14.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>187</v>
       </c>
@@ -4452,7 +4469,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="14.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>187</v>
       </c>
@@ -4481,7 +4498,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="14.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>187</v>
       </c>
@@ -4516,7 +4533,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="14.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>187</v>
       </c>
@@ -4548,7 +4565,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="14.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>187</v>
       </c>
@@ -4577,7 +4594,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="14.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>187</v>
       </c>
@@ -4606,7 +4623,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="14.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>187</v>
       </c>
@@ -4638,7 +4655,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="14.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>187</v>
       </c>
@@ -4670,7 +4687,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="14.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>187</v>
       </c>
@@ -4699,7 +4716,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="14.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>187</v>
       </c>
@@ -4728,7 +4745,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="14.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>187</v>
       </c>
@@ -4757,7 +4774,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="14.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>187</v>
       </c>
@@ -4789,7 +4806,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="14.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>187</v>
       </c>
@@ -4821,7 +4838,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="14.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>187</v>
       </c>
@@ -4847,7 +4864,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="14.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>187</v>
       </c>
@@ -4873,7 +4890,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="14.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>361</v>
       </c>
@@ -4893,7 +4910,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="14.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>361</v>
       </c>
@@ -4913,7 +4930,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="14.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>361</v>
       </c>
@@ -4933,7 +4950,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="14.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>361</v>
       </c>
@@ -4953,7 +4970,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="14.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>361</v>
       </c>
@@ -4973,7 +4990,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="14.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>361</v>
       </c>
@@ -4993,7 +5010,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="14.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>361</v>
       </c>
@@ -5010,7 +5027,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="14.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>361</v>
       </c>
@@ -5027,7 +5044,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="14.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>361</v>
       </c>
@@ -5044,7 +5061,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="14.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>361</v>
       </c>
@@ -5061,7 +5078,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="14.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>361</v>
       </c>
@@ -5078,7 +5095,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="14.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>361</v>
       </c>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8945F34-9C1D-422A-B7B6-3F68F0ED75A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3361CABC-519F-4E3F-9473-3451D882C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3696,10 +3696,10 @@
         <v>2</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G65" t="s">
         <v>24</v>
@@ -3731,10 +3731,10 @@
         <v>2</v>
       </c>
       <c r="E66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66">
-        <v>0.02</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G66" t="s">
         <v>24</v>
@@ -3766,10 +3766,10 @@
         <v>2</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F67">
-        <v>2.5000000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="G67" t="s">
         <v>24</v>
@@ -3798,13 +3798,13 @@
         <v>174</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F68">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G68" t="s">
         <v>20</v>
@@ -4014,7 +4014,7 @@
         <v>3</v>
       </c>
       <c r="F74">
-        <v>1.4999999999999999E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G74" t="s">
         <v>24</v>
@@ -4043,13 +4043,13 @@
         <v>190</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F75">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G75" t="s">
         <v>24</v>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3361CABC-519F-4E3F-9473-3451D882C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AC7333-561B-4829-9D54-03F35D28F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,13 +3868,13 @@
         <v>180</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F70">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G70" t="s">
         <v>24</v>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\antigravity\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AC7333-561B-4829-9D54-03F35D28F4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C8D3D6F-55EE-46B8-90BB-E8F846B069B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2726,19 +2726,22 @@
         <v>102</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G36" t="s">
         <v>24</v>
       </c>
       <c r="H36">
         <v>3</v>
+      </c>
+      <c r="I36">
+        <v>0.4</v>
       </c>
       <c r="J36">
         <v>3</v>
@@ -2758,19 +2761,22 @@
         <v>105</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E37">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G37" t="s">
         <v>24</v>
       </c>
       <c r="H37">
         <v>3</v>
+      </c>
+      <c r="I37">
+        <v>0.4</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2790,19 +2796,22 @@
         <v>107</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G38" t="s">
         <v>24</v>
       </c>
       <c r="H38">
         <v>3</v>
+      </c>
+      <c r="I38">
+        <v>0.4</v>
       </c>
       <c r="J38">
         <v>3</v>
@@ -2822,19 +2831,22 @@
         <v>109</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E39">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G39" t="s">
         <v>24</v>
       </c>
       <c r="H39">
         <v>3</v>
+      </c>
+      <c r="I39">
+        <v>0.4</v>
       </c>
       <c r="J39">
         <v>3</v>
@@ -2854,19 +2866,22 @@
         <v>111</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G40" t="s">
         <v>24</v>
       </c>
       <c r="H40">
         <v>3</v>
+      </c>
+      <c r="I40">
+        <v>0.4</v>
       </c>
       <c r="J40">
         <v>3</v>
@@ -2886,19 +2901,22 @@
         <v>113</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="F41">
-        <v>5.0000000000000001E-3</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G41" t="s">
         <v>24</v>
       </c>
       <c r="H41">
         <v>3</v>
+      </c>
+      <c r="I41">
+        <v>0.4</v>
       </c>
       <c r="J41">
         <v>3</v>
@@ -2918,19 +2936,22 @@
         <v>115</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>2</v>
       </c>
       <c r="F42">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G42" t="s">
         <v>24</v>
       </c>
       <c r="H42">
         <v>3</v>
+      </c>
+      <c r="I42">
+        <v>0.4</v>
       </c>
       <c r="J42">
         <v>3</v>
@@ -2950,19 +2971,22 @@
         <v>118</v>
       </c>
       <c r="D43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G43" t="s">
         <v>24</v>
       </c>
       <c r="H43">
         <v>3</v>
+      </c>
+      <c r="I43">
+        <v>0.4</v>
       </c>
       <c r="J43">
         <v>3</v>
@@ -2982,19 +3006,22 @@
         <v>120</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>2</v>
       </c>
       <c r="F44">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G44" t="s">
         <v>24</v>
       </c>
       <c r="H44">
         <v>3</v>
+      </c>
+      <c r="I44">
+        <v>0.4</v>
       </c>
       <c r="J44">
         <v>3</v>
@@ -3014,19 +3041,22 @@
         <v>122</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>2</v>
       </c>
       <c r="F45">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G45" t="s">
         <v>24</v>
       </c>
       <c r="H45">
         <v>3</v>
+      </c>
+      <c r="I45">
+        <v>0.4</v>
       </c>
       <c r="J45">
         <v>3</v>
@@ -3046,19 +3076,22 @@
         <v>124</v>
       </c>
       <c r="D46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E46">
         <v>2</v>
       </c>
       <c r="F46">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G46" t="s">
         <v>24</v>
       </c>
       <c r="H46">
         <v>3</v>
+      </c>
+      <c r="I46">
+        <v>0.4</v>
       </c>
       <c r="J46">
         <v>3</v>
@@ -3078,19 +3111,22 @@
         <v>126</v>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E47">
         <v>2</v>
       </c>
       <c r="F47">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="G47" t="s">
         <v>24</v>
       </c>
       <c r="H47">
         <v>3</v>
+      </c>
+      <c r="I47">
+        <v>0.4</v>
       </c>
       <c r="J47">
         <v>3</v>
@@ -3594,19 +3630,22 @@
         <v>161</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F62">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G62" t="s">
         <v>24</v>
       </c>
       <c r="H62">
         <v>3</v>
+      </c>
+      <c r="I62">
+        <v>0.8</v>
       </c>
       <c r="J62">
         <v>4</v>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5191,280 +5191,480 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">piercingFocus</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">凝鋒穿刺</t>
         </is>
       </c>
       <c r="D120">
-        <v>25</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">突刺的長度 +30%、寬度 -15%，且造成的傷害 +30%。</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thrust</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thrustLenPct":30,"thrustWidthPct":-15,"skillDamagePct":30}</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">thousandWounds</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">千瘡百孔</t>
         </is>
       </c>
       <c r="D121">
-        <v>18</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">每次突刺命中使敵人受到的傷害 +4%，持續 5 秒，最多疊加 10 層。</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thrust</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thrustVuln":{"pct":4,"dur":5,"maxStacks":10}}</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">sunpiercerLance</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">貫日之刺</t>
         </is>
       </c>
       <c r="D122">
-        <v>15</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">八方連刺改為朝前方的 1 道巨型突刺，突刺範圍 +100%，且造成的傷害 +100%。</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thrust</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"octaToSingle":true,"thrustRangePct":100,"skillDamagePct":100}</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">thunderStab</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">迅雷穿刺</t>
         </is>
       </c>
       <c r="D123">
-        <v>30</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">每次突刺擊中敵人時有 15% 機率附加 1 道連鎖閃電。</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thrust</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thrustChain":{"chance":15,"powerPct":50,"elem":"lightning","bounces":5,"tickSec":0.3,"label":"迅雷穿刺"}}</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">heartrendBleed</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">穿心裂血</t>
         </is>
       </c>
       <c r="D124">
-        <v>25</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">突刺會附加流血，每 0.5 秒造成 50% 物理傷害，持續 5 秒。</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thrust</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thrustDot":{"tickPowerPct":50,"tickSec":0.5,"dur":5}}</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">chainSpin</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">連環迴旋</t>
         </is>
       </c>
       <c r="D125">
-        <v>25</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">迴旋斬的斬擊次數 +2 次。</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cleave</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"cleaveSlashAdd":2}</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">galeBladeDance</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">旋風劍舞</t>
         </is>
       </c>
       <c r="D126">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">迴旋斬的每次斬擊會同時產生旋風，對周圍 8 米範圍內的所有敵人造成 100% 風系傷害。</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cleave</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"cleaveWhirl":{"m":8,"powerPct":100,"elem":"wind"}}</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">skyrendSlash</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">裂空飛斬</t>
         </is>
       </c>
       <c r="D127">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">迴旋斬的斬擊會向外飛出 60 米，命中路徑上的敵人。</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cleave</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"cleaveFlyM":60}</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">exploitWeakness</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">乘虛之斬</t>
         </is>
       </c>
       <c r="D128">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">迴旋斬對暈眩中的敵人造成額外的 50% 傷害。</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cleave</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"cleaveStunnedDmgPct":50}</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">gatheringVortex</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">聚敵旋渦</t>
         </is>
       </c>
       <c r="D129">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">迴旋斬會將 60 米內的所有敵人拉近至身邊 10 米範圍內。</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cleave</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"cleavePull":{"m":60,"toM":10}}</t>
         </is>
       </c>
     </row>
@@ -5476,20 +5676,25 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -5501,18 +5706,293 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D131">
+        <v>18</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D132">
+        <v>15</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D133">
+        <v>30</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D134">
+        <v>25</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D135">
+        <v>25</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D136">
+        <v>12</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D137">
+        <v>15</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D138">
+        <v>8</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D139">
+        <v>30</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D140">
+        <v>5</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D131">
+      <c r="D141">
         <v>35</v>
       </c>
-      <c r="N131" t="inlineStr">
+      <c r="N141" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -5671,280 +5671,480 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">knifeChain</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">連鎖</t>
         </is>
       </c>
       <c r="D130">
-        <v>25</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">飛刀的彈射數 +2 次。</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">knife</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"knifeBounceAdd":2}</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">knifeSplitter</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">分裂者</t>
         </is>
       </c>
       <c r="D131">
-        <v>18</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">飛刀殺死敵人時會分裂出 2 把小型飛刀，每把造成 50% 傷害，且可彈射 2 次。</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">knife</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"knifeSplit":{"count":2,"pct":50,"bounces":2}}</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">knifeExecutioner</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">處刑者</t>
         </is>
       </c>
       <c r="D132">
-        <v>15</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">飛刀會優先在生命值最高的目標間彈射，且對其造成的傷害 +30%。</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">knife</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"knifeExecutor":{"pct":30}}</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">knifeShadowblade</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">影刃</t>
         </is>
       </c>
       <c r="D133">
-        <v>30</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">射出的飛刀數量 +2 把。</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">knife</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"knifeCountAdd":2}</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">knifeWaltzblade</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">輪舞刃</t>
         </is>
       </c>
       <c r="D134">
-        <v>25</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">射出的第 1 把飛刀不再彈射，改為圍繞在你周圍 10 米處旋轉，對路徑上的所有敵人造成傷害，持續 5 秒。</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">knife</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dagger1h</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"knifeOrbit":{"m":10,"sec":5}}</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">galeWhirlwind</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">風捲殘雲</t>
         </is>
       </c>
       <c r="D135">
-        <v>25</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">疾風斬命中時有 35% 機率在目標處形成一道龍捲風，造成 4 段、每段 100% 風系傷害。</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gale</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"galeTornado":{"chance":35,"hits":4,"pct":100,"m":4,"gap":0.4}}</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">galeExecute</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">斬殺</t>
         </is>
       </c>
       <c r="D136">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">疾風斬有 35% 機率可立即殺死生命值 20% 以下的非 BOSS 敵人。</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gale</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"galeExecute":{"chance":35,"hpPct":20}}</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">galeTwinShadow</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">雙影</t>
         </is>
       </c>
       <c r="D137">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">疾風斬命中時有 50% 機率額外對附近 1 個敵人造成 50% 傷害。</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gale</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"galeTwin":{"chance":50,"pct":50,"m":10}}</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">galeWindwalker</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">風行者</t>
         </is>
       </c>
       <c r="D138">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">疾風斬命中時附加風切狀態：移動速度 -80%、命中率 -50%，且每 0.5 秒受到 50% 風系傷害，持續 4 秒。</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gale</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"galeWindRend":{"cutPct":50}}</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">galeGodspeed</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">神速斬</t>
         </is>
       </c>
       <c r="D139">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">疾風斬每次命中時，疾風斬的冷卻時間 -0.1 秒。</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gale</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"galeCdrSec":0.1}</t>
         </is>
       </c>
     </row>
@@ -5956,20 +6156,25 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -5981,18 +6186,293 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D141">
+        <v>18</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D142">
+        <v>15</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D143">
+        <v>30</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D144">
+        <v>25</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D145">
+        <v>25</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D146">
+        <v>12</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D147">
+        <v>15</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D148">
+        <v>8</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D149">
+        <v>30</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D150">
+        <v>5</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D141">
+      <c r="D151">
         <v>35</v>
       </c>
-      <c r="N141" t="inlineStr">
+      <c r="N151" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -6151,280 +6151,480 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">bloodPoisonBurst</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">毒爆</t>
         </is>
       </c>
       <c r="D140">
-        <v>25</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">血刃斬造成中毒的敵人死亡後留下一灘毒霧，對範圍 6 米內的敵人每 0.5 秒造成 50% 中毒傷害，持續 3 秒。</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poison</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodblade</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword2h</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"bloodPoisonMist":{"m":6,"pct":50,"sec":3,"gap":0.5}}</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">bloodVenomRite</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">毒血祭</t>
         </is>
       </c>
       <c r="D141">
-        <v>18</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">血刃斬的中毒每感染 1 個敵人就使自身生命值 -1%，但造成的中毒與流血傷害提高 50%。</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poison</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodblade</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword2h</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"bloodVenomRite":{"hpPct":1,"pct":50}}</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">bloodMist</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">血霧</t>
         </is>
       </c>
       <c r="D142">
-        <v>15</v>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">血刃斬造成流血的敵人死亡後留下一灘血霧，血霧內的敵人每次受傷都回復你 0.2% 生命值，持續 4 秒。</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodblade</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword2h</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"bloodMistField":{"m":6,"healPct":0.2,"sec":4}}</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">bloodShadow</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">血影</t>
         </is>
       </c>
       <c r="D143">
-        <v>30</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">血刃斬有 35% 機率揮出第 2 斬。</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodblade</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword2h</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"bloodSecondSlash":{"chance":35}}</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">bloodCleaver</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">切割</t>
         </is>
       </c>
       <c r="D144">
-        <v>25</v>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">血刃斬的斬擊傷害 +100%。</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodblade</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword2h</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"bloodSlashPct":100}</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">danceFrenzy</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">狂舞</t>
         </is>
       </c>
       <c r="D145">
-        <v>25</v>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">暴風之舞持續期間，每施放 1 次雙刀亂舞就使下一次的施放間隔縮短 6%。</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dualdance</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"danceStormGap":{"pct":6}}</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">danceBerserker</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">狂戰士</t>
         </is>
       </c>
       <c r="D146">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">鐵血之舞造成的生命損失與傷害同時提高 50%。</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dualdance</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"danceIronAmp":{"pct":50}}</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">danceUnyielding</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">不屈之誓</t>
         </is>
       </c>
       <c r="D147">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">暴風之舞持續期間你的死亡延後 10 秒才生效，且這 10 秒內你的傷害提高 100%。</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dualdance</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"danceDeathDefer":{"sec":10,"pct":100}}</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">danceThousandCuts</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">殺千刀</t>
         </is>
       </c>
       <c r="D148">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">雙刀亂舞每殺死 1 個敵人就使暴風之舞的持續時間 +0.2 秒。</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dualdance</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"danceStormKill":{"sec":0.2}}</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">danceTwinBlades</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">雙生刃</t>
         </is>
       </c>
       <c r="D149">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">雙刀亂舞的擊中目標數量 +2 個。</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dualdance</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"danceTargetAdd":{"count":2}}</t>
         </is>
       </c>
     </row>
@@ -6436,20 +6636,25 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D150">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -6461,18 +6666,293 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D151">
+        <v>18</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D152">
+        <v>15</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D153">
+        <v>30</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D154">
+        <v>25</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D155">
+        <v>25</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D156">
+        <v>12</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D157">
+        <v>15</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D158">
+        <v>8</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D159">
+        <v>30</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D160">
+        <v>5</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D151">
+      <c r="D161">
         <v>35</v>
       </c>
-      <c r="N151" t="inlineStr">
+      <c r="N161" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -6631,280 +6631,480 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">counterOath</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">堅韌誓言</t>
         </is>
       </c>
       <c r="D150">
-        <v>25</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">反擊 100 次後獲得無敵狀態，持續 3 秒。</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">counter</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"counterOath":{"count":100,"sec":3}}</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">counterWrath</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">怒火</t>
         </is>
       </c>
       <c r="D151">
-        <v>18</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">反擊 100 次後獲得怒火狀態，造成的傷害提高 30%，持續 6 秒。</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">counter</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"counterWrath":{"count":100,"pct":30,"sec":6}}</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">counterPerfect</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">完美姿態</t>
         </is>
       </c>
       <c r="D152">
-        <v>15</v>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">每次反擊有 10% 機率造成完美反擊，該次反擊傷害提高 300%。</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">counter</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"counterPerfect":{"chance":10,"pct":300}}</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">counterBloodPay</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">以血還血</t>
         </is>
       </c>
       <c r="D153">
-        <v>30</v>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">每次反擊損失自身 1% 生命值，但反擊傷害提高 50%。</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">counter</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"counterBloodPay":{"hpPct":1,"pct":50}}</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">counterWindBody</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">風之體</t>
         </is>
       </c>
       <c r="D154">
-        <v>25</v>
-      </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">反擊有 10% 機率朝目標射出一道風刃，造成 100% 普攻傷害的風系傷害。</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">counter</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"counterWindBlade":{"chance":10,"powerPct":100}}</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">rageValor</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">英勇氣概</t>
         </is>
       </c>
       <c r="D155">
-        <v>25</v>
-      </c>
-      <c r="M155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">嗜血狂怒的攻速額外 +30%（與本體同為突破上限的乘算）。</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rageAspdPct":30}</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">rageBurnBlood</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">燃血</t>
         </is>
       </c>
       <c r="D156">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">【血飲術】每造成 1 次自身生命損失就使你造成的傷害 +1%，最多疊 50 層，持續 4 秒。</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rageBurnBlood":{"pct":1,"maxStacks":50,"sec":4}}</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">rageBloodDebt</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">血債償還</t>
         </is>
       </c>
       <c r="D157">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">【血飲術】造成的自身生命損失降低 50%。</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rageSelfCut":{"reducePct":50}}</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">rageZealot</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">狂熱者</t>
         </is>
       </c>
       <c r="D158">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">每 0.1 連擊數使【狂血盛宴】的傷害加成再提高 5%（＝每 1 連擊數 +50%）。</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rageZealotPct":50}</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">rageSlaughterer</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">屠戮者</t>
         </is>
       </c>
       <c r="D159">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">狂怒期間每殺死 1 個敵人使【嗜血反震】的效果提高 5%，最多疊 10 層，持續 4 秒。</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">phys</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bloodrage</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greatsword2h</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rageThornsStack":{"pct":5,"maxStacks":10,"sec":4}}</t>
         </is>
       </c>
     </row>
@@ -6916,20 +7116,25 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D160">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -6941,18 +7146,293 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D161">
+        <v>18</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D162">
+        <v>15</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D163">
+        <v>30</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D164">
+        <v>25</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D165">
+        <v>25</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D166">
+        <v>12</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D167">
+        <v>15</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D168">
+        <v>8</v>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D169">
+        <v>30</v>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D170">
+        <v>5</v>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D161">
+      <c r="D171">
         <v>35</v>
       </c>
-      <c r="N161" t="inlineStr">
+      <c r="N171" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -7111,280 +7111,480 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">fireballBeadShot</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">連珠火</t>
         </is>
       </c>
       <c r="D160">
-        <v>25</v>
-      </c>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">火球及殞石的數量 +1 個。</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fireball</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"fireballCountAdd":{"count":1}}</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">fireballEmber</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">燃燼</t>
         </is>
       </c>
       <c r="D161">
-        <v>18</v>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">火球術造成的燃燒效果傷害 +50%。</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fireball</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"fireballBurnDmgPct":50}</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">fireballPool</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">火池</t>
         </is>
       </c>
       <c r="D162">
-        <v>15</v>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">火球及殞石爆炸後會在地上留下一團半徑 6 米的火池，每 0.5 秒對範圍內的敵人造成 50% 火焰傷害，持續 4 秒。</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fireball</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firePool":{"m":6,"pct":50,"gap":0.5,"sec":4}}</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">fireballHeart</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">烈焰之心</t>
         </is>
       </c>
       <c r="D163">
-        <v>30</v>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">火球及殞石對燃燒狀態的敵人造成的傷害 +30%。</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fireball</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"fireballBurningDmgPct":30}</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">fireballBurst</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">爆裂</t>
         </is>
       </c>
       <c r="D164">
-        <v>25</v>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">【火球爆裂】會額外產生 3 個小火球。</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fireball</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"fireballSplitAdd":{"count":3}}</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">firepillarTracking</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">追蹤烈焰</t>
         </is>
       </c>
       <c r="D165">
-        <v>25</v>
-      </c>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">火龍捲會追蹤敵人，移動速度 12 米／秒。</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firepillar</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firepillarChase":{"mps":12,"m":30}}</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">firepillarSpread</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">火龍擴散</t>
         </is>
       </c>
       <c r="D166">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">火龍捲的體積增加 30%。</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firepillar</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firepillarScalePct":30}</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">firepillarOutburst</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">火焰爆衝</t>
         </is>
       </c>
       <c r="D167">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">火龍捲的傷害段數 +3 段。</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firepillar</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firepillarHitsAdd":{"hits":3}}</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">firepillarDeflagration</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">爆燃</t>
         </is>
       </c>
       <c r="D168">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">火龍捲每造成 1 段傷害就使該敵人受到的燃燒傷害 +10%。</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firepillar</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firepillarBurnAmp":{"pct":10}}</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">firepillarResonance</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">火龍共鳴</t>
         </is>
       </c>
       <c r="D169">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">場上每存在 1 道火龍捲，所有火龍捲造成的傷害 +4%。</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firepillar</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firepillarResonancePct":4}</t>
         </is>
       </c>
     </row>
@@ -7396,20 +7596,25 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -7421,18 +7626,293 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D171">
+        <v>18</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D172">
+        <v>15</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D173">
+        <v>30</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D174">
+        <v>25</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D175">
+        <v>25</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D176">
+        <v>12</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D177">
+        <v>15</v>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D178">
+        <v>8</v>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D179">
+        <v>30</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D180">
+        <v>5</v>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D171">
+      <c r="D181">
         <v>35</v>
       </c>
-      <c r="N171" t="inlineStr">
+      <c r="N181" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -7591,280 +7591,480 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">firehuntAmplify</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">增焰</t>
         </is>
       </c>
       <c r="D170">
-        <v>25</v>
-      </c>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">火狩的體積與環繞半徑 +25%。</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firehuntScalePct":25}</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">firehuntConcurrent</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">伴生併發</t>
         </is>
       </c>
       <c r="D171">
-        <v>18</v>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">每 1 秒，你的 1 團火狩會飛出攻擊半徑 20 米內的敵人，對目標 10 米內的所有敵人造成 300% 火焰傷害。</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firehuntLaunch":{"gap":1,"m":20,"aoeM":10,"pct":300}}</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">firehuntBlaze</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">烈火狩</t>
         </is>
       </c>
       <c r="D172">
-        <v>15</v>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">在火狩的持續時間內，每 0.5 秒你的火焰傷害提高 2%（火狩全部消失後結束）。</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firehuntFireAmp":{"gap":0.5,"pct":2}}</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">firehuntDetonate</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">炎爆</t>
         </is>
       </c>
       <c r="D173">
-        <v>30</v>
-      </c>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">一個敵人被火狩命中 10 次後會爆炸，對其周圍 6 米內的敵人造成 250% 火焰傷害。</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firehuntDetonate":{"hits":10,"m":6,"pct":250}}</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">firehuntHunter</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">狩獵者</t>
         </is>
       </c>
       <c r="D174">
-        <v>25</v>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">你的火狩數量減半（無條件進位，至少 1 團），但造成的傷害額外 +150%。</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fire</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">firehunt</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"firehuntHunter":{"pct":150}}</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">rockHeavyArmor</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">重岩甲</t>
         </is>
       </c>
       <c r="D175">
-        <v>25</v>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">岩甲術獲得的生命護盾 +30%。</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rockShieldPct":30}</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">rockLightArmor</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">輕飛甲</t>
         </is>
       </c>
       <c r="D176">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">岩甲護盾存在期間，你的移動速度 +30%。</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rockMoveSpeedPct":30}</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">rockAmpBoost</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">巨岩增幅</t>
         </is>
       </c>
       <c r="D177">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">【岩甲增幅】可疊加的層數 +10 層。</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rockAmpStacksAdd":{"maxStacks":10}}</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">rockSpikeArmor</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">尖刺甲</t>
         </is>
       </c>
       <c r="D178">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">【岩甲尖刺】的效果提高 100%。</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rockSpikePct":100}</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">rockEarthHeart</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">大地之心</t>
         </is>
       </c>
       <c r="D179">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">當你的生命護盾降至 0 時獲得無敵 2 秒；此效果每 30 秒只能觸發 1 次。</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rockarmor</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"rockHeartInvuln":{"sec":2,"cd":30}}</t>
         </is>
       </c>
     </row>
@@ -7876,20 +8076,25 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D180">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -7901,18 +8106,293 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D181">
+        <v>18</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D182">
+        <v>15</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D183">
+        <v>30</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D184">
+        <v>25</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D185">
+        <v>25</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D186">
+        <v>12</v>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D187">
+        <v>15</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D188">
+        <v>8</v>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D189">
+        <v>30</v>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D190">
+        <v>5</v>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C191" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D181">
+      <c r="D191">
         <v>35</v>
       </c>
-      <c r="N181" t="inlineStr">
+      <c r="N191" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -8071,280 +8071,480 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">mireSpread</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">蔓延</t>
         </is>
       </c>
       <c r="D180">
-        <v>25</v>
-      </c>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">泥沼術的範圍 +25%。</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mire</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"mireScalePct":25}</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">mireWeaken</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">削弱</t>
         </is>
       </c>
       <c r="D181">
-        <v>18</v>
-      </c>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">在泥沼術範圍中的敵人造成的傷害 -30%。</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mire</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"mireWeaken":{"reducePct":30}}</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">mireCorrupt</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">腐化</t>
         </is>
       </c>
       <c r="D182">
-        <v>15</v>
-      </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">在泥沼術範圍內所有受到控場的敵人，受到的傷害 +30%。</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mire</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"mireCorruptPct":30}</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">mireLavaBurn</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">熔火</t>
         </is>
       </c>
       <c r="D183">
-        <v>30</v>
-      </c>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">熔岩沼的火焰傷害 +70%。</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mire</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"mireLavaPct":70}</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">mireErode</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">侵蝕</t>
         </is>
       </c>
       <c r="D184">
-        <v>25</v>
-      </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">泥沼術會附加流血，每 0.5 秒造成 150% 物理傷害，持續 5 秒。</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mire</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">magicSword1h</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"mireBleed":{"tickPowerPct":150,"tickSec":0.5,"dur":5}}</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">earthguardManaFeed</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">魔力滋養</t>
         </is>
       </c>
       <c r="D185">
-        <v>25</v>
-      </c>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">大地守護會使溢出的 50% 法力轉為你的生命護盾。</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earthguard</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"egManaOverflowShield":{"pct":50}}</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">earthguardLifeFeed</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">生命滋養</t>
         </is>
       </c>
       <c r="D186">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L186">
+        <v>0</v>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">大地守護會使溢出的 10% 生命轉為你的法力值。</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earthguard</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"egHpOverflowMana":{"pct":10}}</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">earthguardSoulLink</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">靈魂連結</t>
         </is>
       </c>
       <c r="D187">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">【生命反射之盾】可以額外對 1 個敵人產生作用。</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earthguard</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"egReflectAdd":{"count":1}}</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">earthguardHeartOfEarth</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">地之心</t>
         </is>
       </c>
       <c r="D188">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">每殺死 1 個敵人，【天地共生】的復活冷卻時間 -1 秒。</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earthguard</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"egKillCdr":{"sec":1}}</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">earthguardUndyingWill</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">不滅意志</t>
         </is>
       </c>
       <c r="D189">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">【天地共生】復活後的無敵時間內，每殺死 1 個敵人則無敵時間 +0.5 秒。</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earth</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earthguard</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"egKillInvuln":{"sec":0.5}}</t>
         </is>
       </c>
     </row>
@@ -8356,20 +8556,25 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D190">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -8381,18 +8586,293 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D191">
+        <v>18</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D192">
+        <v>15</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D193">
+        <v>30</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D194">
+        <v>25</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D195">
+        <v>25</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D196">
+        <v>12</v>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D197">
+        <v>15</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D198">
+        <v>8</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D199">
+        <v>30</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D200">
+        <v>5</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C201" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D191">
+      <c r="D201">
         <v>35</v>
       </c>
-      <c r="N191" t="inlineStr">
+      <c r="N201" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -8551,280 +8551,480 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">chainlightningSurge</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">電荷連鎖</t>
         </is>
       </c>
       <c r="D190">
-        <v>25</v>
-      </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">連鎖閃電的彈射數 +2 次。</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chainLinkAdd":{"count":2}}</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">chainlightningVolley</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">電擊</t>
         </is>
       </c>
       <c r="D191">
-        <v>18</v>
-      </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">連鎖閃電的發射數量 +2 道。</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chainBoltAdd":{"count":2}}</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">chainlightningScatter</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">雷散落</t>
         </is>
       </c>
       <c r="D192">
-        <v>15</v>
-      </c>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">【電殛擴散】額外對 1 個敵人造成傷害，且其傷害提高 50%。</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chainSplashAdd":{"count":1},"chainSplashPct":50}</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">chainlightningSuper</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">超導</t>
         </is>
       </c>
       <c r="D193">
-        <v>30</v>
-      </c>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">連鎖閃電每彈射 1 次，該道閃電鏈的傷害 +10%。</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chainBouncePct":10}</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">chainlightningOverload</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">過載</t>
         </is>
       </c>
       <c r="D194">
-        <v>25</v>
-      </c>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">同一個敵人受到 5 次連鎖閃電的彈射後產生爆炸，對周圍 6 米內的敵人造成 200% 雷電傷害。</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chainlightning</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sword1h</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"chainOverload":{"hits":5,"m":6,"pct":200}}</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">thunderstrikeTriple</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">三重雷</t>
         </is>
       </c>
       <c r="D195">
-        <v>25</v>
-      </c>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">【雙重落雷】的攻擊次數 +1 次。</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderHitAdd":{"count":1}}</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">thunderstrikeLock</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">雷鎖</t>
         </is>
       </c>
       <c r="D196">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">落雷術額外攻擊 1 個目標。</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderTargetAdd":{"count":1}}</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">thunderstrikeQuake</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">震雷</t>
         </is>
       </c>
       <c r="D197">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">被落雷術擊中的敵人暈眩時間 +1 秒，且其在暈眩狀態下受到的傷害 +25%。</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderStunAdd":{"sec":1},"thunderStunnedVulnPct":25}</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">thunderstrikeRebirth</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">雷之再生</t>
         </is>
       </c>
       <c r="D198">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">【迅雷重生】的機率提高至 100%。</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderRegenTo":{"chance":100}}</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">thunderstrikeRod</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">引雷針</t>
         </is>
       </c>
       <c r="D199">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">落雷術會優先攻擊 24 米內生命值最低的敵人，且對其造成的傷害提高 20%。</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderstrike</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderRod":{"m":24,"pct":20}}</t>
         </is>
       </c>
     </row>
@@ -8836,20 +9036,25 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D200">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -8861,18 +9066,293 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D201">
+        <v>18</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D202">
+        <v>15</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D203">
+        <v>30</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D204">
+        <v>25</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D205">
+        <v>25</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D206">
+        <v>12</v>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D207">
+        <v>15</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D208">
+        <v>8</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D209">
+        <v>30</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D210">
+        <v>5</v>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D201">
+      <c r="D211">
         <v>35</v>
       </c>
-      <c r="N201" t="inlineStr">
+      <c r="N211" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -9031,280 +9031,480 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">thunderorbCore</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">雷核</t>
         </is>
       </c>
       <c r="D200">
-        <v>25</v>
-      </c>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">雷球的體積增大 30%。</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderorbScalePct":30}</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">thunderorbOverload</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">超載</t>
         </is>
       </c>
       <c r="D201">
-        <v>18</v>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">場上每擁有 1 個雷球，你的雷電傷害 +3%。</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderorbFieldAmpPct":3}</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">thunderorbShockCore</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">感電核心</t>
         </is>
       </c>
       <c r="D202">
-        <v>15</v>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">【伴生雷球】的持續時間增加 100%。</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderorbCompanionSecPct":100}</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">thunderorbFallCount</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">雷殞落</t>
         </is>
       </c>
       <c r="D203">
-        <v>30</v>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">【雷殞天落】降下的雷球數量 +1 顆。</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderorbFallAdd":{"count":1}}</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">thunderorbFallStun</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">雷殞震</t>
         </is>
       </c>
       <c r="D204">
-        <v>25</v>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">被【雷殞天落】降下的雷球擊中的敵人會暈眩 4 秒。</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lightning</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thunderorb</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">orb</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"thunderorbFallStunTo":{"sec":4}}</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">icearrowVolley</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">連射</t>
         </is>
       </c>
       <c r="D205">
-        <v>25</v>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">寒冰箭射出數量 +2 支。</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icearrow</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spellbook</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"icearrowCountAdd":{"count":2}}</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">icearrowSeal</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">冰封</t>
         </is>
       </c>
       <c r="D206">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">寒冰箭傷害 +50%。</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icearrow</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spellbook</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"icearrowDamagePct":50}</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">icearrowWinter</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">凜冬侵蝕</t>
         </is>
       </c>
       <c r="D207">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">寒冰箭造成的寒霜狀態傷害與持續時間 +50%。</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icearrow</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spellbook</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"icearrowFrostPct":50}</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">icearrowSplit</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">冰裂箭</t>
         </is>
       </c>
       <c r="D208">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">寒冰箭擊中敵人後會再分裂出 2 支小型寒冰箭，向前方的敵人造成 150% 寒冰傷害。</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icearrow</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spellbook</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"icearrowSplit":{"count":2,"pct":150}}</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">icearrowDeepFreeze</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">深度凍結</t>
         </is>
       </c>
       <c r="D209">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">寒冰箭擊中暈眩或凍結的敵人造成的傷害 +50%。</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">icearrow</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spellbook</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"icearrowControlPct":50}</t>
         </is>
       </c>
     </row>
@@ -9316,20 +9516,25 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D210">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -9341,18 +9546,293 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D211">
+        <v>18</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D212">
+        <v>15</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D213">
+        <v>30</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D214">
+        <v>25</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D215">
+        <v>25</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D216">
+        <v>12</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D217">
+        <v>15</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D218">
+        <v>8</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D219">
+        <v>30</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D220">
+        <v>5</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D211">
+      <c r="D221">
         <v>35</v>
       </c>
-      <c r="N211" t="inlineStr">
+      <c r="N221" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -9511,280 +9511,480 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">waterballVolley</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">水流連彈</t>
         </is>
       </c>
       <c r="D210">
-        <v>25</v>
-      </c>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">水流彈的發射數量 +2 顆。</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waterball</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"waterballShotAdd":{"count":2}}</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">waterballNovaBurst</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">冰霜擴散</t>
         </is>
       </c>
       <c r="D211">
-        <v>18</v>
-      </c>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">【寒流爆散】的擴散爆炸變成冰霜新星，且範圍增大 30%。</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waterball</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"waterballBurstNova":{"scalePct":30}}</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">waterballFrostSurge</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">寒霜湧動</t>
         </is>
       </c>
       <c r="D212">
-        <v>15</v>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">水流彈造成的寒霜狀態可在凍結後再疊加 5 層，每層再增加 50% 寒冰傷害。</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waterball</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"waterballFrostOver":{"count":5,"pct":50}}</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">waterballTorrent</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">激流</t>
         </is>
       </c>
       <c r="D213">
-        <v>30</v>
-      </c>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">水流彈的彈射次數 +2 次，且彈射速度 +30%。</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waterball</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"waterballBounceAdd":{"count":2},"waterballBounceSpeedPct":30}</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">waterballTornado</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">水龍勢</t>
         </is>
       </c>
       <c r="D214">
-        <v>25</v>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>0</v>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">水流彈擊中時有 10% 機率在目標處形成 1 道水龍捲，造成 4 段 100% 寒冰傷害。</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waterball</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"waterballTornadoProc":{"chance":10,"hits":4,"pct":100}}</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">frostnovaShatter</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">碎冰</t>
         </is>
       </c>
       <c r="D215">
-        <v>25</v>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">冰霜新星的攻擊範圍 +30%。</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frostnova</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"frostnovaScalePct":30}</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">frostnovaTwinBurst</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">雙冰爆</t>
         </is>
       </c>
       <c r="D216">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">冰霜新星擊中帶有寒霜狀態的敵人時，有 35% 機率在目標處再爆發 1 次冰霜新星。</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frostnova</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"frostnovaTwinBurst":{"chance":35}}</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">frostnovaIceSpike</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">寒冰衝擊</t>
         </is>
       </c>
       <c r="D217">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">冰霜新星殺死被凍結的敵人時，會在目標地面昇起 1 根冰錐，對周圍 8 米內的敵人造成 4 段 100% 寒冰傷害。</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frostnova</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"frostnovaKillSpike":{"hits":4,"pct":100,"m":8}}</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">frostnovaColdTide</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">寒潮</t>
         </is>
       </c>
       <c r="D218">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">冰霜新星擊中帶有寒霜狀態的敵人時，有 20% 機率在目標處再爆發 1 次冰霜新星。</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frostnova</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"frostnovaColdTide":{"chance":20}}</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">frostnovaWinterFrost</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">凜冬寒霜</t>
         </is>
       </c>
       <c r="D219">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">暴風雪持續時間內會不斷對範圍內的敵人施加寒霜狀態，且寒霜狀態傷害 +30%。</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ice</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frostnova</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">staff2h</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"frostnovaBlizzardFrost":{"stacks":1},"frostnovaFrostDmgPct":30}</t>
         </is>
       </c>
     </row>
@@ -9796,20 +9996,25 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D220">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -9821,18 +10026,293 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D221">
+        <v>18</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D222">
+        <v>15</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D223">
+        <v>30</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D224">
+        <v>25</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D225">
+        <v>25</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D226">
+        <v>12</v>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D227">
+        <v>15</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D228">
+        <v>8</v>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D229">
+        <v>30</v>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D230">
+        <v>5</v>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C231" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D221">
+      <c r="D231">
         <v>35</v>
       </c>
-      <c r="N221" t="inlineStr">
+      <c r="N231" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -9628,7 +9628,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">水流彈造成的寒霜狀態可在凍結後再疊加 5 層，每層再增加 50% 寒冰傷害。</t>
+          <t xml:space="preserve">水流彈造成的寒霜狀態可在凍結後再疊加 5 層；寒霜凍傷依目前寒霜總層數計算。</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -9991,280 +9991,480 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">windbladeRend</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">裂風</t>
         </is>
       </c>
       <c r="D220">
-        <v>25</v>
-      </c>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">風刃每擊中敵人 1 次則傷害額外 +5%，最高為 +100%。</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">windblade</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"windbladeRamp":{"pct":5,"max":100}}</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">windbladePressure</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">增壓</t>
         </is>
       </c>
       <c r="D221">
-        <v>18</v>
-      </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">風刃的體積增大 25%，且飛行速度 +30%。</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">windblade</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"windbladeSizePct":25,"windbladeSpeedPct":30}</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">windbladeTrace</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">風之痕</t>
         </is>
       </c>
       <c r="D222">
-        <v>15</v>
-      </c>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">【亂披風】會在風刃另一側額外射出 1 道小型風刃，且小型風刃傷害 +30%。</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">windblade</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"windbladeSmallMirror":{"count":1},"windbladeSmallDmgPct":30}</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">windbladeErode</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">風蝕</t>
         </is>
       </c>
       <c r="D223">
-        <v>30</v>
-      </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">風刃擊中敵人時會附加風蝕狀態，讓敵人受到的傷害 +25%，持續 4 秒。</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">windblade</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"windbladeErode":{"pct":25,"sec":4}}</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">windbladeVoidCut</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">斷空刃</t>
         </is>
       </c>
       <c r="D224">
-        <v>25</v>
-      </c>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">【暴風真空刃】每個方向改為連續射出 3 道風刃，且風刃傷害額外 +30%。</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">windblade</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wand1h</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"windbladeVolleyTo":{"count":3},"windbladeDmgPct":30}</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">vacuumResonance</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">共振</t>
         </is>
       </c>
       <c r="D225">
-        <v>25</v>
-      </c>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">【真空爆震】會額外多造成 1 次傷害。</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">axe2h</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"vacuumBurstAdd":{"hits":1}}</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">vacuumRift</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">裂痕</t>
         </is>
       </c>
       <c r="D226">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">真空斬造成的風切狀態疊加層數 +3 層。</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">axe2h</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"vacuumRendStacks":{"maxStacks":3}}</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">vacuumWindBlade</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">真空風刃</t>
         </is>
       </c>
       <c r="D227">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">每次施放真空斬會額外射出 2 道小型風刃。</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">axe2h</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"vacuumSmallBlades":{"count":2}}</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">vacuumExpand</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">空間澎脹</t>
         </is>
       </c>
       <c r="D228">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">真空斬的體積 +25%。</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">axe2h</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"vacuumScalePct":25}</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">vacuumFlux</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">虛空漲落</t>
         </is>
       </c>
       <c r="D229">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">【虛空斬】的持續時間 +3 秒。</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vacuumslash</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">axe2h</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"vacuumVoidSec":{"sec":3}}</t>
         </is>
       </c>
     </row>
@@ -10276,20 +10476,25 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D230">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hpPct</t>
+        </is>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -10301,18 +10506,293 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
+          <t xml:space="preserve">godMight</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神力</t>
+        </is>
+      </c>
+      <c r="D231">
+        <v>18</v>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godHaste</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神速</t>
+        </is>
+      </c>
+      <c r="D232">
+        <v>15</v>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godSlayer</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">屠神</t>
+        </is>
+      </c>
+      <c r="D233">
+        <v>30</v>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">greed</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">貪婪</t>
+        </is>
+      </c>
+      <c r="D234">
+        <v>25</v>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">godWall</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神壁</t>
+        </is>
+      </c>
+      <c r="D235">
+        <v>25</v>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D236">
+        <v>12</v>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D237">
+        <v>15</v>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D238">
+        <v>8</v>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D239">
+        <v>30</v>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D240">
+        <v>5</v>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D231">
+      <c r="D241">
         <v>35</v>
       </c>
-      <c r="N231" t="inlineStr">
+      <c r="N241" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>

--- a/config/Excel/Equipment_Affix.xlsx
+++ b/config/Excel/Equipment_Affix.xlsx
@@ -10471,150 +10471,240 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t xml:space="preserve">dragonBlood</t>
+          <t xml:space="preserve">stormbarrierAbsorb</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t xml:space="preserve">龍血</t>
+          <t xml:space="preserve">吸收</t>
         </is>
       </c>
       <c r="D230">
-        <v>25</v>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hpPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t xml:space="preserve">生命上限提高 {v}%</t>
+          <t xml:space="preserve">暴風屏障的傷害減免 +10%。</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"stormbarrierRedPct":10}</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t xml:space="preserve">godMight</t>
+          <t xml:space="preserve">stormbarrierReflect</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t xml:space="preserve">神力</t>
+          <t xml:space="preserve">暴風反射</t>
         </is>
       </c>
       <c r="D231">
-        <v>18</v>
-      </c>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">atkPct;matkPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
+          <t xml:space="preserve">【暴風之刃】射出風刃的機率 +10%。</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"stormbladeChanceAdd":{"chance":10}}</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t xml:space="preserve">godHaste</t>
+          <t xml:space="preserve">stormbarrierCounterCut</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t xml:space="preserve">神速</t>
+          <t xml:space="preserve">逆風切</t>
         </is>
       </c>
       <c r="D232">
-        <v>15</v>
-      </c>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t xml:space="preserve">aspdPct</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊速度提高 {v}%</t>
+          <t xml:space="preserve">【亂風切】所附加的風切狀態，每層傷害 +35%。</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"stormRendDmgPct":35}</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t xml:space="preserve">godSlayer</t>
+          <t xml:space="preserve">stormbarrierWall</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">屠神</t>
+          <t xml:space="preserve">風之壁</t>
         </is>
       </c>
       <c r="D233">
-        <v>30</v>
-      </c>
-      <c r="M233" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eliteDmg;bossDmg</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
+          <t xml:space="preserve">暴風屏障作用中，你的物理與魔法防禦額外 +20%。</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"stormbarrierDefPct":20}</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t xml:space="preserve">神鑄特效</t>
+          <t xml:space="preserve">傳奇特效</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t xml:space="preserve">greed</t>
+          <t xml:space="preserve">stormbarrierCore</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">貪婪</t>
+          <t xml:space="preserve">風暴核心</t>
         </is>
       </c>
       <c r="D234">
-        <v>25</v>
-      </c>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t xml:space="preserve">goldBonus;loot</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
+          <t xml:space="preserve">【暴風神體】的持續時間 +50%。</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wind</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stormbarrier</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shield</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"stormGodSecPct":50}</t>
         </is>
       </c>
     </row>
@@ -10626,12 +10716,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t xml:space="preserve">godWall</t>
+          <t xml:space="preserve">dragonBlood</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">神壁</t>
+          <t xml:space="preserve">龍血</t>
         </is>
       </c>
       <c r="D235">
@@ -10639,12 +10729,12 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">defPct;mdefPct</t>
+          <t xml:space="preserve">hpPct</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
+          <t xml:space="preserve">生命上限提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -10656,20 +10746,25 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t xml:space="preserve">smite</t>
+          <t xml:space="preserve">godMight</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">天罰</t>
+          <t xml:space="preserve">神力</t>
         </is>
       </c>
       <c r="D236">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">atkPct;matkPct</t>
+        </is>
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+          <t xml:space="preserve">物理與魔法攻擊額外提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -10681,20 +10776,25 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t xml:space="preserve">annihilate</t>
+          <t xml:space="preserve">godHaste</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">破滅</t>
+          <t xml:space="preserve">神速</t>
         </is>
       </c>
       <c r="D237">
         <v>15</v>
       </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">aspdPct</t>
+        </is>
+      </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+          <t xml:space="preserve">攻擊速度提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -10706,20 +10806,25 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctuary</t>
+          <t xml:space="preserve">godSlayer</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">聖佑</t>
+          <t xml:space="preserve">屠神</t>
         </is>
       </c>
       <c r="D238">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eliteDmg;bossDmg</t>
+        </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+          <t xml:space="preserve">對菁英與BOSS傷害提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -10731,20 +10836,25 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t xml:space="preserve">undying</t>
+          <t xml:space="preserve">greed</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">不朽</t>
+          <t xml:space="preserve">貪婪</t>
         </is>
       </c>
       <c r="D239">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">goldBonus;loot</t>
+        </is>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+          <t xml:space="preserve">金幣加成與掉寶率提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -10756,20 +10866,25 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t xml:space="preserve">omniDrain</t>
+          <t xml:space="preserve">godWall</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">萬象汲取</t>
+          <t xml:space="preserve">神壁</t>
         </is>
       </c>
       <c r="D240">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">defPct;mdefPct</t>
+        </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+          <t xml:space="preserve">物理與魔法防禦提高 {v}%</t>
         </is>
       </c>
     </row>
@@ -10781,18 +10896,143 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
+          <t xml:space="preserve">smite</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天罰</t>
+        </is>
+      </c>
+      <c r="D241">
+        <v>12</v>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時有 {v}% 機率降下神雷，造成 250% 物理攻擊的真實傷害</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">annihilate</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">破滅</t>
+        </is>
+      </c>
+      <c r="D242">
+        <v>15</v>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">暴擊時有 {v}% 機率使本次傷害翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanctuary</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">聖佑</t>
+        </is>
+      </c>
+      <c r="D243">
+        <v>8</v>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到的所有傷害降低 {v}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">undying</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不朽</t>
+        </is>
+      </c>
+      <c r="D244">
+        <v>30</v>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">受到致命攻擊時有 {v}% 機率保留 1 點生命並回復 30% 最大生命（60 秒內限一次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">omniDrain</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">萬象汲取</t>
+        </is>
+      </c>
+      <c r="D245">
+        <v>5</v>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">攻擊時額外回復造成傷害 {v}% 的生命與法力</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">神鑄特效</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
           <t xml:space="preserve">godWrath</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t xml:space="preserve">神怒</t>
         </is>
       </c>
-      <c r="D241">
+      <c r="D246">
         <v>35</v>
       </c>
-      <c r="N241" t="inlineStr">
+      <c r="N246" t="inlineStr">
         <is>
           <t xml:space="preserve">生命低於 30% 時，造成的傷害提高 {v}%</t>
         </is>
